--- a/docs/internships.xlsx
+++ b/docs/internships.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nmilner\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E92148-1737-4225-986B-6FC1CED53D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,39 +25,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="88">
   <si>
     <t xml:space="preserve">Firm Name   </t>
   </si>
   <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEPA Loc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A &amp; E Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arch and Eng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilkes-Barre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highland Associates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarks Summit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.highlandassociates.com/</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>NEPA Loc</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>A &amp; E Group</t>
+  </si>
+  <si>
+    <t>Arch and Eng</t>
+  </si>
+  <si>
+    <t>Wilkes-Barre</t>
+  </si>
+  <si>
+    <t>Highland Associates</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Clarks Summit</t>
+  </si>
+  <si>
+    <t>https://www.highlandassociates.com/</t>
   </si>
   <si>
     <t xml:space="preserve">Precision Pipeline LLC </t>
@@ -61,7 +66,7 @@
     <t xml:space="preserve">Constr and Util </t>
   </si>
   <si>
-    <t xml:space="preserve">Wyalusing</t>
+    <t>Wyalusing</t>
   </si>
   <si>
     <t xml:space="preserve">Sordoni Construction </t>
@@ -70,7 +75,7 @@
     <t xml:space="preserve">Construction </t>
   </si>
   <si>
-    <t xml:space="preserve">Forty Fort</t>
+    <t>Forty Fort</t>
   </si>
   <si>
     <t xml:space="preserve">The LiRo Group </t>
@@ -79,7 +84,7 @@
     <t xml:space="preserve">Eng and Constr </t>
   </si>
   <si>
-    <t xml:space="preserve">Scranton</t>
+    <t>Scranton</t>
   </si>
   <si>
     <t xml:space="preserve">Barry Isett and Associates </t>
@@ -88,7 +93,7 @@
     <t xml:space="preserve">Engineering </t>
   </si>
   <si>
-    <t xml:space="preserve">Multiple</t>
+    <t>Multiple</t>
   </si>
   <si>
     <t xml:space="preserve">Borton-Lawson (Verdantas) </t>
@@ -100,7 +105,7 @@
     <t xml:space="preserve">Foth Engineering </t>
   </si>
   <si>
-    <t xml:space="preserve">Mehoopany</t>
+    <t>Mehoopany</t>
   </si>
   <si>
     <t xml:space="preserve">GAI Consultants </t>
@@ -112,25 +117,25 @@
     <t xml:space="preserve">LaBella Associates  </t>
   </si>
   <si>
-    <t xml:space="preserve">Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dunmore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penn Eastern, LCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pennoni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plains</t>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Dunmore</t>
+  </si>
+  <si>
+    <t>Penn Eastern, LCC</t>
+  </si>
+  <si>
+    <t>Pennoni</t>
+  </si>
+  <si>
+    <t>Plains</t>
   </si>
   <si>
     <t xml:space="preserve">Trimech </t>
   </si>
   <si>
-    <t xml:space="preserve">Philadelphia</t>
+    <t>Philadelphia</t>
   </si>
   <si>
     <t xml:space="preserve">Gentex </t>
@@ -139,13 +144,13 @@
     <t xml:space="preserve">Government </t>
   </si>
   <si>
-    <t xml:space="preserve">Carbondale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lockheed Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archibald</t>
+    <t>Carbondale</t>
+  </si>
+  <si>
+    <t>Lockheed Martin</t>
+  </si>
+  <si>
+    <t>Archibald</t>
   </si>
   <si>
     <t xml:space="preserve">Guyette Communication Industries </t>
@@ -154,13 +159,13 @@
     <t xml:space="preserve">Manuf and Util </t>
   </si>
   <si>
-    <t xml:space="preserve">Plymouth</t>
+    <t>Plymouth</t>
   </si>
   <si>
     <t xml:space="preserve">Northeast Data, Inc </t>
   </si>
   <si>
-    <t xml:space="preserve">Tunkhannock</t>
+    <t>Tunkhannock</t>
   </si>
   <si>
     <t xml:space="preserve">Alleima </t>
@@ -172,130 +177,130 @@
     <t xml:space="preserve">Ashley Machine &amp; Tool </t>
   </si>
   <si>
-    <t xml:space="preserve">West Wyoming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canpack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olyphant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CornellCookson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mountain Top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crystal Window &amp; Door Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diamond Manufacturing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wyoming Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynco Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloomsburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">General Dynamics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMS Pilling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greiner Packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pittston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAM Works LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mayfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lions Brewery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOSCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olympia Chimney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procter &amp; Gamble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pulverman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronco Machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abington</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towanda Metadyne, Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US Hydrations</t>
+    <t>West Wyoming</t>
+  </si>
+  <si>
+    <t>Canpack</t>
+  </si>
+  <si>
+    <t>Olyphant</t>
+  </si>
+  <si>
+    <t>CornellCookson</t>
+  </si>
+  <si>
+    <t>Mountain Top</t>
+  </si>
+  <si>
+    <t>Crystal Window &amp; Door Systems</t>
+  </si>
+  <si>
+    <t>Dalton</t>
+  </si>
+  <si>
+    <t>Diamond Manufacturing</t>
+  </si>
+  <si>
+    <t>Wyoming Area</t>
+  </si>
+  <si>
+    <t>Dynco Inc.</t>
+  </si>
+  <si>
+    <t>Bloomsburg</t>
+  </si>
+  <si>
+    <t>General Dynamics</t>
+  </si>
+  <si>
+    <t>GMS Pilling</t>
+  </si>
+  <si>
+    <t>Greiner Packaging</t>
+  </si>
+  <si>
+    <t>Pittston</t>
+  </si>
+  <si>
+    <t>JAM Works LLC</t>
+  </si>
+  <si>
+    <t>Mayfield</t>
+  </si>
+  <si>
+    <t>Lions Brewery</t>
+  </si>
+  <si>
+    <t>MOSCA</t>
+  </si>
+  <si>
+    <t>Hazelton</t>
+  </si>
+  <si>
+    <t>Olympia Chimney</t>
+  </si>
+  <si>
+    <t>Procter &amp; Gamble</t>
+  </si>
+  <si>
+    <t>Pulverman</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Ronco Machine</t>
+  </si>
+  <si>
+    <t>Abington</t>
+  </si>
+  <si>
+    <t>Towanda Metadyne, Inc</t>
+  </si>
+  <si>
+    <t>Towanda</t>
+  </si>
+  <si>
+    <t>US Hydrations</t>
   </si>
   <si>
     <t xml:space="preserve">Linde Corporation </t>
   </si>
   <si>
-    <t xml:space="preserve">Utility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Southwestern Energy</t>
+    <t>Utility</t>
+  </si>
+  <si>
+    <t>Southwestern Energy</t>
+  </si>
+  <si>
+    <t>https://www.aegroupinc.net/</t>
+  </si>
+  <si>
+    <t>https://sordoni.com/sordoni-about-us/project-engineering-internships/</t>
+  </si>
+  <si>
+    <t>https://www.liro.com/careers/</t>
+  </si>
+  <si>
+    <t>https://careers.gaiconsultants.com/internships/</t>
+  </si>
+  <si>
+    <t>https://www.northeastdata.com/</t>
+  </si>
+  <si>
+    <t>https://www.alleima.com/en/careers/students/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -312,7 +317,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -320,58 +325,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -413,14 +391,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -473,485 +451,501 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38.67"/>
+    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="61.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="D6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="D11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="D20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="B23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="B38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
